--- a/data/trans_orig/IP25A_R_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP25A_R_2023-Estudios-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que emplean 2 horas o más en ver la televisión en 2023 (tasa de respuesta: 98,91%)</t>
+          <t>Menores según si emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión en 2023 (tasa de respuesta: 98,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11570</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7062</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17657</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>20,57%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>12,55%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>31,39%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>10238</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5296</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>21059</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>20,07%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,38%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>41,28%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13335</t>
+          <t>7950</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>4149</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19317</t>
+          <t>12912</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>23572</t>
+          <t>19520</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16255</t>
+          <t>13261</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34428</t>
+          <t>27432</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>27,54%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>44688</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>38601</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>49196</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>79,43%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>68,61%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>87,45%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>40782</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>29961</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>45724</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>79,93%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>58,72%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>89,62%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>48091</t>
+          <t>35396</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42109</t>
+          <t>30434</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53528</t>
+          <t>39197</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>88874</t>
+          <t>80084</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>78018</t>
+          <t>72172</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>96191</t>
+          <t>86343</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>86,69%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56258</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56258</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56258</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>51020</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>51020</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>51020</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61426</t>
+          <t>43346</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61426</t>
+          <t>43346</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61426</t>
+          <t>43346</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>112446</t>
+          <t>99604</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>112446</t>
+          <t>99604</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>112446</t>
+          <t>99604</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>62016</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>48502</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>74538</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13,1%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>10,25%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>15,75%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>59349</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>45510</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>75256</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>13,09%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>10,04%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>16,6%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>67481</t>
+          <t>55473</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53567</t>
+          <t>45633</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82199</t>
+          <t>69552</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>126831</t>
+          <t>117489</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>107707</t>
+          <t>101534</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>146441</t>
+          <t>138724</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,44%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>563</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>411208</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>398686</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>424722</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>86,9%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>84,25%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>89,75%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>549</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>393931</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>378024</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>407770</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>86,91%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>83,4%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>89,96%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>563</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>446538</t>
+          <t>369717</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>431820</t>
+          <t>355638</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>460452</t>
+          <t>379557</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>840469</t>
+          <t>780925</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>820859</t>
+          <t>759690</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>859593</t>
+          <t>796880</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,7%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>473224</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>473224</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>473224</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>634</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>453280</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>453280</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>453280</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514019</t>
+          <t>425190</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514019</t>
+          <t>425190</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514019</t>
+          <t>425190</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>967300</t>
+          <t>898414</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>967300</t>
+          <t>898414</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>967300</t>
+          <t>898414</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>22424</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>15208</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>33149</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13,31%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>9,03%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>19,68%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>20142</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>14090</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>28951</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13,57%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,49%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19,5%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>23509</t>
+          <t>20513</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15222</t>
+          <t>14871</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32709</t>
+          <t>29187</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>43652</t>
+          <t>42937</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33258</t>
+          <t>32613</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56380</t>
+          <t>54765</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,25%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>145995</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>135270</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>153211</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>86,69%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>80,32%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>90,97%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>199</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>128330</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>119521</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>134382</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>86,43%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>80,5%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>90,51%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>159840</t>
+          <t>128523</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>150640</t>
+          <t>119849</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>168127</t>
+          <t>134165</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>288169</t>
+          <t>274518</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>275441</t>
+          <t>262690</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>298563</t>
+          <t>284842</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,73%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>148472</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>148472</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>148472</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149036</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149036</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149036</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>331821</t>
+          <t>317455</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>331821</t>
+          <t>317455</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>331821</t>
+          <t>317455</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>96010</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>81248</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>112983</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13,76%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11,64%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>16,19%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>89729</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>72595</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>107776</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>13,75%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>11,12%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>16,51%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>104325</t>
+          <t>83936</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87401</t>
+          <t>71092</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>123075</t>
+          <t>98544</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>194055</t>
+          <t>179946</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>170618</t>
+          <t>159662</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>221940</t>
+          <t>202970</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,43%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>601891</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>584918</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>616653</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>86,24%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>83,81%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>88,36%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>800</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>563043</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>544996</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>580177</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>86,25%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>83,49%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>88,88%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>840</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>654469</t>
+          <t>533636</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>635719</t>
+          <t>519028</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>671393</t>
+          <t>546480</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1217512</t>
+          <t>1135527</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1189627</t>
+          <t>1112503</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1240949</t>
+          <t>1155811</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,86%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>972</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>697901</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>697901</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>697901</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>925</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>652772</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>652772</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>652772</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>972</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>758794</t>
+          <t>617572</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>758794</t>
+          <t>617572</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>758794</t>
+          <t>617572</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1411567</t>
+          <t>1315473</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1411567</t>
+          <t>1315473</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1411567</t>
+          <t>1315473</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
